--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileCostChangeTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileCostChangeTemplate.xlsx
@@ -29,9 +29,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -56,6 +63,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -77,6 +90,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -90,6 +109,25 @@
   </si>
   <si>
     <r>
+      <t>分摊重量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(KG)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -112,6 +150,9 @@
   </si>
   <si>
     <t>期末暂估费用(¥)</t>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
   <si>
     <t>2025-03</t>
@@ -1095,7 +1136,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.5" style="2" customWidth="1"/>
@@ -1103,15 +1144,15 @@
     <col min="3" max="3" width="20.25" style="2" customWidth="1"/>
     <col min="4" max="4" width="17.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.375" style="2" customWidth="1"/>
-    <col min="6" max="7" width="17.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.25" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14.75" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="6" max="8" width="17.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15.25" style="2" customWidth="1"/>
+    <col min="12" max="12" width="14.75" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:13">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1130,10 +1171,10 @@
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="7" t="s">
@@ -1144,16 +1185,22 @@
       </c>
       <c r="K1" s="7" t="s">
         <v>10</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576">
       <formula1>"运费,关税,其他税费,其他费用"</formula1>
     </dataValidation>
   </dataValidations>

--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileCostChangeTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileCostChangeTemplate.xlsx
@@ -109,6 +109,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>分摊重量</t>
     </r>
     <r>
@@ -155,7 +160,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>2025-03</t>
+    <t>2025-01</t>
   </si>
 </sst>
 </file>
